--- a/pipeline/credit_rating/output/xhtn_tong_hop_20261028.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20261028.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1827,7 +1827,7 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1915,7 +1915,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2379,7 +2379,7 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2963,7 +2963,7 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3535,7 +3535,7 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3623,7 +3623,7 @@
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4655,7 +4655,7 @@
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5207,7 +5207,7 @@
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6307,7 +6307,7 @@
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6429,7 +6429,7 @@
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7075,7 +7075,7 @@
       <c r="AD59" t="inlineStr"/>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7159,7 +7159,7 @@
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8415,7 +8415,7 @@
       <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8503,7 +8503,7 @@
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9073,7 +9073,7 @@
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9299,7 +9299,7 @@
       <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14139,7 +14139,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15355,7 +15355,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16485,7 +16485,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16599,7 +16599,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -16825,7 +16825,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -16941,7 +16941,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17161,7 +17161,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17639,7 +17639,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18481,7 +18481,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -18933,7 +18933,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19395,7 +19395,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19511,7 +19511,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20333,7 +20333,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20665,7 +20665,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -20903,7 +20903,7 @@
       <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21143,7 +21143,7 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21367,7 +21367,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21701,7 +21701,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22037,7 +22037,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22149,7 +22149,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22607,7 +22607,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -22837,7 +22837,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23065,7 +23065,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23185,7 +23185,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23411,7 +23411,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23635,7 +23635,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -23749,7 +23749,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24193,7 +24193,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24303,7 +24303,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24531,7 +24531,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24659,7 +24659,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -24897,7 +24897,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25007,7 +25007,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25127,7 +25127,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25351,7 +25351,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25479,7 +25479,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25601,7 +25601,7 @@
       <c r="AD221" t="inlineStr"/>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -25845,7 +25845,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -25973,7 +25973,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26105,7 +26105,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26219,7 +26219,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26341,7 +26341,7 @@
       <c r="AD227" t="inlineStr"/>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26453,7 +26453,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26553,7 +26553,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26663,7 +26663,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -26895,7 +26895,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27247,7 +27247,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27361,7 +27361,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27475,7 +27475,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27585,7 +27585,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27699,7 +27699,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -27921,7 +27921,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28037,7 +28037,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28153,7 +28153,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28265,7 +28265,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28489,7 +28489,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28617,7 +28617,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -28847,7 +28847,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -28969,7 +28969,7 @@
       <c r="AD250" t="inlineStr"/>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29095,7 +29095,7 @@
       <c r="AD251" t="inlineStr"/>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29221,7 +29221,7 @@
       <c r="AD252" t="inlineStr"/>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29565,7 +29565,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29799,7 +29799,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -29919,7 +29919,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30029,7 +30029,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30249,7 +30249,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30365,7 +30365,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30493,7 +30493,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30605,7 +30605,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30717,7 +30717,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30831,7 +30831,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -30941,7 +30941,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31051,7 +31051,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31163,7 +31163,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31273,7 +31273,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31393,7 +31393,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31509,7 +31509,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31625,7 +31625,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31753,7 +31753,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31865,7 +31865,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -31977,7 +31977,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32089,7 +32089,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32205,7 +32205,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32315,7 +32315,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32435,7 +32435,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32545,7 +32545,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32665,7 +32665,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32775,7 +32775,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -32885,7 +32885,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -32995,7 +32995,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33105,7 +33105,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33219,7 +33219,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33329,7 +33329,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33441,7 +33441,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33551,7 +33551,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33783,7 +33783,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -33893,7 +33893,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34017,7 +34017,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34141,7 +34141,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34251,7 +34251,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34471,7 +34471,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34583,7 +34583,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34693,7 +34693,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -34803,7 +34803,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -34931,7 +34931,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35037,7 +35037,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35265,7 +35265,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35381,7 +35381,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35491,7 +35491,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35601,7 +35601,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35717,7 +35717,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -35833,7 +35833,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -35943,7 +35943,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36059,7 +36059,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36169,7 +36169,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36279,7 +36279,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36389,7 +36389,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36489,7 +36489,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36711,7 +36711,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -36821,7 +36821,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -36941,7 +36941,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37053,7 +37053,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37163,7 +37163,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37275,7 +37275,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37391,7 +37391,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37503,7 +37503,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37613,7 +37613,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -37729,7 +37729,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -37839,7 +37839,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -37965,7 +37965,7 @@
       <c r="AD329" t="inlineStr"/>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38093,7 +38093,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38205,7 +38205,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38305,7 +38305,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38405,7 +38405,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38519,7 +38519,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38633,7 +38633,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -38733,7 +38733,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -38853,7 +38853,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -38965,7 +38965,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39077,7 +39077,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39301,7 +39301,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39411,7 +39411,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39543,7 +39543,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39671,7 +39671,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -39927,7 +39927,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40039,7 +40039,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40151,7 +40151,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40261,7 +40261,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40371,7 +40371,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40499,7 +40499,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40609,7 +40609,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -40737,7 +40737,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -40849,7 +40849,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -40961,7 +40961,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41071,7 +41071,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41191,7 +41191,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41315,7 +41315,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41439,7 +41439,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41563,7 +41563,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41675,7 +41675,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -41791,7 +41791,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -41903,7 +41903,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42031,7 +42031,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42159,7 +42159,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42271,7 +42271,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42383,7 +42383,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42493,7 +42493,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42603,7 +42603,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42719,7 +42719,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -42831,7 +42831,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -42951,7 +42951,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43195,7 +43195,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43295,7 +43295,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43407,7 +43407,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43535,7 +43535,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43659,7 +43659,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43769,7 +43769,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -43879,7 +43879,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -43989,7 +43989,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44099,7 +44099,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44219,7 +44219,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44329,7 +44329,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44439,7 +44439,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44549,7 +44549,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44669,7 +44669,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -44789,7 +44789,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -44909,7 +44909,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45029,7 +45029,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45145,7 +45145,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45261,7 +45261,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45377,7 +45377,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45489,7 +45489,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45601,7 +45601,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45721,7 +45721,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45833,7 +45833,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -45949,7 +45949,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46059,7 +46059,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:52</t>
+          <t>2026-10-28 15:22:11</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46169,7 +46169,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46285,7 +46285,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46397,7 +46397,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46507,7 +46507,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46619,7 +46619,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46731,7 +46731,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46843,7 +46843,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -46963,7 +46963,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47091,7 +47091,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47211,7 +47211,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47339,7 +47339,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47451,7 +47451,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47561,7 +47561,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47671,7 +47671,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47783,7 +47783,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47895,7 +47895,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48005,7 +48005,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48121,7 +48121,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48231,7 +48231,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48343,7 +48343,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48453,7 +48453,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48563,7 +48563,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48691,7 +48691,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48803,7 +48803,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -48931,7 +48931,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49043,7 +49043,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49153,7 +49153,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49263,7 +49263,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49373,7 +49373,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49485,7 +49485,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49595,7 +49595,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49723,7 +49723,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49835,7 +49835,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -49945,7 +49945,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50055,7 +50055,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50165,7 +50165,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50275,7 +50275,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50385,7 +50385,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50497,7 +50497,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50625,7 +50625,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50735,7 +50735,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -50845,7 +50845,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -50957,7 +50957,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51067,7 +51067,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51179,7 +51179,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51307,7 +51307,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51417,7 +51417,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51529,7 +51529,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51639,7 +51639,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51749,7 +51749,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -51859,7 +51859,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -51959,7 +51959,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52069,7 +52069,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52169,7 +52169,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52279,7 +52279,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52407,7 +52407,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52517,7 +52517,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52627,7 +52627,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -52737,7 +52737,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -52847,7 +52847,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -52957,7 +52957,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53067,7 +53067,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53177,7 +53177,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53287,7 +53287,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53415,7 +53415,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53527,7 +53527,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53627,7 +53627,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53737,7 +53737,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -53851,7 +53851,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -53961,7 +53961,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54061,7 +54061,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54173,7 +54173,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54285,7 +54285,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54395,7 +54395,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54507,7 +54507,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54619,7 +54619,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -54729,7 +54729,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -54857,7 +54857,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -54989,7 +54989,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55121,7 +55121,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55253,7 +55253,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55377,7 +55377,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55489,7 +55489,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55589,7 +55589,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55709,7 +55709,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -55825,7 +55825,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -55937,7 +55937,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56059,7 +56059,7 @@
       <c r="AD487" t="inlineStr"/>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56171,7 +56171,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56281,7 +56281,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56391,7 +56391,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56501,7 +56501,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56611,7 +56611,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56739,7 +56739,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56855,7 +56855,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -56965,7 +56965,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57093,7 +57093,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57221,7 +57221,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57349,7 +57349,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57477,7 +57477,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57589,7 +57589,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57699,7 +57699,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57827,7 +57827,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57939,7 +57939,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58051,7 +58051,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58167,7 +58167,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58279,7 +58279,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58391,7 +58391,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58503,7 +58503,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58615,7 +58615,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58735,7 +58735,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58845,7 +58845,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -58973,7 +58973,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59093,7 +59093,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59205,7 +59205,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59317,7 +59317,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59417,7 +59417,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59533,7 +59533,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59643,7 +59643,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59755,7 +59755,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59865,7 +59865,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -59977,7 +59977,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60089,7 +60089,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60189,7 +60189,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60299,7 +60299,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60411,7 +60411,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60521,7 +60521,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60631,7 +60631,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60743,7 +60743,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60853,7 +60853,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -60963,7 +60963,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61073,7 +61073,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61193,7 +61193,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61317,7 +61317,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61427,7 +61427,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61539,7 +61539,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61649,7 +61649,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61761,7 +61761,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61873,7 +61873,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -61983,7 +61983,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62093,7 +62093,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62203,7 +62203,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62313,7 +62313,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62423,7 +62423,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62533,7 +62533,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62645,7 +62645,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62757,7 +62757,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62869,7 +62869,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -62979,7 +62979,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63091,7 +63091,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63191,7 +63191,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63301,7 +63301,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63401,7 +63401,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63501,7 +63501,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63613,7 +63613,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63725,7 +63725,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63837,7 +63837,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -63947,7 +63947,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64057,7 +64057,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64167,7 +64167,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64279,7 +64279,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64389,7 +64389,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64499,7 +64499,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64609,7 +64609,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64719,7 +64719,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64831,7 +64831,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -64943,7 +64943,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65059,7 +65059,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65187,7 +65187,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65299,7 +65299,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65409,7 +65409,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65529,7 +65529,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65639,7 +65639,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65749,7 +65749,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65859,7 +65859,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -65979,7 +65979,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66095,7 +66095,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66207,7 +66207,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66327,7 +66327,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66439,7 +66439,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66539,7 +66539,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66659,7 +66659,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66769,7 +66769,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66881,7 +66881,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -66997,7 +66997,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67109,7 +67109,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67221,7 +67221,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67349,7 +67349,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67459,7 +67459,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67569,7 +67569,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67679,7 +67679,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67791,7 +67791,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67919,7 +67919,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68031,7 +68031,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68143,7 +68143,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68255,7 +68255,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68355,7 +68355,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68465,7 +68465,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68575,7 +68575,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68675,7 +68675,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68785,7 +68785,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68913,7 +68913,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69023,7 +69023,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69135,7 +69135,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69245,7 +69245,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69357,7 +69357,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69467,7 +69467,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69577,7 +69577,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69677,7 +69677,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69787,7 +69787,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69899,7 +69899,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70009,7 +70009,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70119,7 +70119,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70229,7 +70229,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70339,7 +70339,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70449,7 +70449,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70559,7 +70559,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70659,7 +70659,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70769,7 +70769,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70879,7 +70879,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -70991,7 +70991,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71101,7 +71101,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71213,7 +71213,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71323,7 +71323,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71433,7 +71433,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71543,7 +71543,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71653,7 +71653,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71763,7 +71763,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71875,7 +71875,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -71985,7 +71985,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72097,7 +72097,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72209,7 +72209,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72319,7 +72319,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72431,7 +72431,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72543,7 +72543,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72653,7 +72653,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72763,7 +72763,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72873,7 +72873,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -72983,7 +72983,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73083,7 +73083,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73195,7 +73195,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73305,7 +73305,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73415,7 +73415,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73543,7 +73543,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73655,7 +73655,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73767,7 +73767,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73895,7 +73895,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -74007,7 +74007,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74135,7 +74135,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74263,7 +74263,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:43</t>
+          <t>2026-10-28 15:22:01</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74375,7 +74375,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74487,7 +74487,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74597,7 +74597,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74709,7 +74709,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74819,7 +74819,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74929,7 +74929,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -75041,7 +75041,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75153,7 +75153,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75265,7 +75265,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75375,7 +75375,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75485,7 +75485,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75597,7 +75597,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75709,7 +75709,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75819,7 +75819,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75931,7 +75931,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -76041,7 +76041,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76141,7 +76141,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76251,7 +76251,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76363,7 +76363,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76473,7 +76473,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76585,7 +76585,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76695,7 +76695,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76805,7 +76805,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76915,7 +76915,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -77025,7 +77025,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77135,7 +77135,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77247,7 +77247,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77357,7 +77357,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77467,7 +77467,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77577,7 +77577,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77689,7 +77689,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77799,7 +77799,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77911,7 +77911,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -78023,7 +78023,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -78123,7 +78123,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78233,7 +78233,7 @@
       </c>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78345,7 +78345,7 @@
       </c>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78457,7 +78457,7 @@
       </c>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78569,7 +78569,7 @@
       </c>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
@@ -78681,7 +78681,7 @@
       </c>
       <c r="AE689" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF689" t="inlineStr">
@@ -78791,7 +78791,7 @@
       </c>
       <c r="AE690" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF690" t="inlineStr">
@@ -78901,7 +78901,7 @@
       </c>
       <c r="AE691" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF691" t="inlineStr">
@@ -79013,7 +79013,7 @@
       </c>
       <c r="AE692" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF692" t="inlineStr">
@@ -79123,7 +79123,7 @@
       </c>
       <c r="AE693" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF693" t="inlineStr">
@@ -79235,7 +79235,7 @@
       </c>
       <c r="AE694" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF694" t="inlineStr">
@@ -79335,7 +79335,7 @@
       </c>
       <c r="AE695" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF695" t="inlineStr">
@@ -79445,7 +79445,7 @@
       </c>
       <c r="AE696" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF696" t="inlineStr">
@@ -79557,7 +79557,7 @@
       </c>
       <c r="AE697" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF697" t="inlineStr">
@@ -79667,7 +79667,7 @@
       <c r="AD698" t="inlineStr"/>
       <c r="AE698" t="inlineStr">
         <is>
-          <t>2026-10-28 09:59:07</t>
+          <t>2026-10-28 15:22:26</t>
         </is>
       </c>
       <c r="AF698" t="inlineStr">
@@ -79779,7 +79779,7 @@
       </c>
       <c r="AE699" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF699" t="inlineStr">
@@ -79891,7 +79891,7 @@
       </c>
       <c r="AE700" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF700" t="inlineStr">
@@ -80001,7 +80001,7 @@
       </c>
       <c r="AE701" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF701" t="inlineStr">
@@ -80113,7 +80113,7 @@
       </c>
       <c r="AE702" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF702" t="inlineStr">
@@ -80213,7 +80213,7 @@
       </c>
       <c r="AE703" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF703" t="inlineStr">
@@ -80313,7 +80313,7 @@
       </c>
       <c r="AE704" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF704" t="inlineStr">
@@ -80413,7 +80413,7 @@
       </c>
       <c r="AE705" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF705" t="inlineStr">
@@ -80525,7 +80525,7 @@
       </c>
       <c r="AE706" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF706" t="inlineStr">
@@ -80625,7 +80625,7 @@
       </c>
       <c r="AE707" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF707" t="inlineStr">
@@ -80735,7 +80735,7 @@
       </c>
       <c r="AE708" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF708" t="inlineStr">
@@ -80835,7 +80835,7 @@
       </c>
       <c r="AE709" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF709" t="inlineStr">
@@ -80947,7 +80947,7 @@
       </c>
       <c r="AE710" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF710" t="inlineStr">
@@ -81059,7 +81059,7 @@
       </c>
       <c r="AE711" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF711" t="inlineStr">
@@ -81171,7 +81171,7 @@
       </c>
       <c r="AE712" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF712" t="inlineStr">
@@ -81283,7 +81283,7 @@
       </c>
       <c r="AE713" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF713" t="inlineStr">
@@ -81383,7 +81383,7 @@
       </c>
       <c r="AE714" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF714" t="inlineStr">
@@ -81495,7 +81495,7 @@
       </c>
       <c r="AE715" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF715" t="inlineStr">
@@ -81605,7 +81605,7 @@
       </c>
       <c r="AE716" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF716" t="inlineStr">
@@ -81717,7 +81717,7 @@
       </c>
       <c r="AE717" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF717" t="inlineStr">
@@ -81817,7 +81817,7 @@
       </c>
       <c r="AE718" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF718" t="inlineStr">
@@ -81917,7 +81917,7 @@
       </c>
       <c r="AE719" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF719" t="inlineStr">
@@ -82017,7 +82017,7 @@
       </c>
       <c r="AE720" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF720" t="inlineStr">
@@ -82117,7 +82117,7 @@
       </c>
       <c r="AE721" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF721" t="inlineStr">
@@ -82229,7 +82229,7 @@
       </c>
       <c r="AE722" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF722" t="inlineStr">
@@ -82341,7 +82341,7 @@
       </c>
       <c r="AE723" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF723" t="inlineStr">
@@ -82441,7 +82441,7 @@
       </c>
       <c r="AE724" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF724" t="inlineStr">
@@ -82551,7 +82551,7 @@
       </c>
       <c r="AE725" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF725" t="inlineStr">
@@ -82663,7 +82663,7 @@
       </c>
       <c r="AE726" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF726" t="inlineStr">
@@ -82775,7 +82775,7 @@
       </c>
       <c r="AE727" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF727" t="inlineStr">
@@ -82887,7 +82887,7 @@
       </c>
       <c r="AE728" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF728" t="inlineStr">
@@ -82999,7 +82999,7 @@
       </c>
       <c r="AE729" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF729" t="inlineStr">
@@ -83111,7 +83111,7 @@
       </c>
       <c r="AE730" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF730" t="inlineStr">
@@ -83223,7 +83223,7 @@
       </c>
       <c r="AE731" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF731" t="inlineStr">
@@ -83335,7 +83335,7 @@
       </c>
       <c r="AE732" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF732" t="inlineStr">
@@ -83435,7 +83435,7 @@
       </c>
       <c r="AE733" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF733" t="inlineStr">
@@ -83535,7 +83535,7 @@
       </c>
       <c r="AE734" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF734" t="inlineStr">
@@ -83647,7 +83647,7 @@
       </c>
       <c r="AE735" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:39</t>
+          <t>2026-10-28 15:21:56</t>
         </is>
       </c>
       <c r="AF735" t="inlineStr">
@@ -83747,7 +83747,7 @@
       </c>
       <c r="AE736" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF736" t="inlineStr">
@@ -83847,7 +83847,7 @@
       </c>
       <c r="AE737" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF737" t="inlineStr">
@@ -83947,7 +83947,7 @@
       </c>
       <c r="AE738" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF738" t="inlineStr">
@@ -84057,7 +84057,7 @@
       </c>
       <c r="AE739" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF739" t="inlineStr">
@@ -84157,7 +84157,7 @@
       </c>
       <c r="AE740" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF740" t="inlineStr">
@@ -84267,7 +84267,7 @@
       </c>
       <c r="AE741" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF741" t="inlineStr">
@@ -84349,7 +84349,7 @@
       <c r="AD742" t="inlineStr"/>
       <c r="AE742" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF742" t="inlineStr">
@@ -84431,7 +84431,7 @@
       <c r="AD743" t="inlineStr"/>
       <c r="AE743" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF743" t="inlineStr">
@@ -84513,7 +84513,7 @@
       <c r="AD744" t="inlineStr"/>
       <c r="AE744" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF744" t="inlineStr">
@@ -84595,7 +84595,7 @@
       <c r="AD745" t="inlineStr"/>
       <c r="AE745" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:47</t>
+          <t>2026-10-28 15:22:06</t>
         </is>
       </c>
       <c r="AF745" t="inlineStr">
